--- a/output/2026-09-08/enriched_analysis.xlsx
+++ b/output/2026-09-08/enriched_analysis.xlsx
@@ -816,10 +816,10 @@
         <v>0.077</v>
       </c>
       <c r="Q2" t="n">
-        <v>2593</v>
+        <v>2571</v>
       </c>
       <c r="R2" t="n">
-        <v>8.91</v>
+        <v>8.85</v>
       </c>
       <c r="S2" t="n">
         <v>36</v>
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.411</v>
+        <v>0.413</v>
       </c>
       <c r="Q3" t="n">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="R3" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="S3" t="n">
         <v>19</v>
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
       <c r="Q4" t="n">
-        <v>17016</v>
+        <v>16846</v>
       </c>
       <c r="R4" t="n">
-        <v>43.3</v>
+        <v>42.9</v>
       </c>
       <c r="S4" t="n">
         <v>83</v>
@@ -1359,13 +1359,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.016</v>
+        <v>2.969</v>
       </c>
       <c r="Q5" t="n">
-        <v>2732</v>
+        <v>2775</v>
       </c>
       <c r="R5" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.058</v>
+        <v>0.056</v>
       </c>
       <c r="Q6" t="n">
-        <v>1403</v>
+        <v>1458</v>
       </c>
       <c r="R6" t="n">
-        <v>18.9</v>
+        <v>19.6</v>
       </c>
       <c r="S6" t="n">
         <v>55</v>
@@ -1726,7 +1726,7 @@
         <v>0.049</v>
       </c>
       <c r="Q7" t="n">
-        <v>15724</v>
+        <v>15730</v>
       </c>
       <c r="R7" t="n">
         <v>19.9</v>
@@ -1905,13 +1905,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.533</v>
+        <v>0.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="R8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="S8" t="n">
         <v>17</v>
@@ -2090,7 +2090,7 @@
         <v>0.006</v>
       </c>
       <c r="Q9" t="n">
-        <v>4285</v>
+        <v>4261</v>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.16</v>
+        <v>0.157</v>
       </c>
       <c r="Q10" t="n">
-        <v>693</v>
+        <v>707</v>
       </c>
       <c r="R10" t="n">
-        <v>57.9</v>
+        <v>59.1</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -2449,13 +2449,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.306</v>
+        <v>0.296</v>
       </c>
       <c r="Q11" t="n">
-        <v>2775</v>
+        <v>2868</v>
       </c>
       <c r="R11" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="S11" t="n">
         <v>8</v>
@@ -2634,7 +2634,7 @@
         <v>0.074</v>
       </c>
       <c r="Q12" t="n">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="R12" t="n">
         <v>13.6</v>
@@ -2816,10 +2816,10 @@
         <v>0.007</v>
       </c>
       <c r="Q13" t="n">
-        <v>5991</v>
+        <v>5916</v>
       </c>
       <c r="R13" t="n">
-        <v>10.1</v>
+        <v>9.99</v>
       </c>
       <c r="S13" t="n">
         <v>43</v>
@@ -2995,13 +2995,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.744</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="R14" t="n">
-        <v>87.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="S14" t="n">
         <v>-1</v>
@@ -3019,7 +3019,7 @@
         <v>-0.18</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y14" t="b">
         <v>0</v>
@@ -3183,7 +3183,7 @@
         <v>432</v>
       </c>
       <c r="R15" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
         <v>21</v>
@@ -3359,13 +3359,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="R16" t="n">
-        <v>8.99</v>
+        <v>8.94</v>
       </c>
       <c r="S16" t="n">
         <v>7</v>
@@ -3541,13 +3541,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.135</v>
+        <v>0.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="R17" t="n">
-        <v>5.99</v>
+        <v>6.23</v>
       </c>
       <c r="S17" t="n">
         <v>118</v>
@@ -3719,13 +3719,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.105</v>
+        <v>0.102</v>
       </c>
       <c r="Q18" t="n">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="R18" t="n">
-        <v>26.6</v>
+        <v>27.3</v>
       </c>
       <c r="S18" t="n">
         <v>24</v>
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="Q19" t="n">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
@@ -4081,13 +4081,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.312</v>
+        <v>0.308</v>
       </c>
       <c r="Q20" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R20" t="n">
-        <v>27.4</v>
+        <v>27.9</v>
       </c>
       <c r="S20" t="n">
         <v>21</v>
@@ -4263,13 +4263,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.505</v>
+        <v>0.502</v>
       </c>
       <c r="Q21" t="n">
-        <v>1112</v>
+        <v>1120</v>
       </c>
       <c r="R21" t="n">
-        <v>56.6</v>
+        <v>57</v>
       </c>
       <c r="S21" t="n">
         <v>21</v>
@@ -4445,13 +4445,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0.183</v>
+        <v>0.191</v>
       </c>
       <c r="Q22" t="n">
-        <v>1646</v>
+        <v>1575</v>
       </c>
       <c r="R22" t="n">
-        <v>57.4</v>
+        <v>54.9</v>
       </c>
       <c r="S22" t="n">
         <v>7</v>
@@ -4627,13 +4627,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.576</v>
+        <v>0.582</v>
       </c>
       <c r="Q23" t="n">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="R23" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S23" t="n">
         <v>22</v>
@@ -4789,33 +4789,33 @@
         <v>14.1</v>
       </c>
       <c r="J24" t="n">
-        <v>12.47</v>
+        <v>12.52</v>
       </c>
       <c r="K24" t="n">
-        <v>13.1</v>
+        <v>12.6</v>
       </c>
       <c r="L24" t="n">
         <v>69.12</v>
       </c>
       <c r="M24" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="N24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.412</v>
+        <v>0.427</v>
       </c>
       <c r="Q24" t="n">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="R24" t="n">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="S24" t="n">
         <v>-61</v>
@@ -4847,10 +4847,10 @@
         <v>2.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>12.43442394576657</v>
+        <v>12.47706136306301</v>
       </c>
       <c r="AE24" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
@@ -4874,53 +4874,53 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="AK24" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
       </c>
       <c r="AM24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AN24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS24" t="n">
-        <v>1623554</v>
+        <v>2172554</v>
       </c>
       <c r="AT24" t="n">
-        <v>4847634</v>
+        <v>5396634</v>
       </c>
       <c r="AU24" t="n">
-        <v>16959087</v>
+        <v>17508087</v>
       </c>
       <c r="AV24" t="n">
-        <v>16959087</v>
+        <v>17508087</v>
       </c>
       <c r="AW24" t="n">
-        <v>16959087</v>
+        <v>17508087</v>
       </c>
       <c r="AX24" t="n">
-        <v>1623554</v>
+        <v>2172554</v>
       </c>
       <c r="AY24" t="n">
-        <v>16959087</v>
+        <v>17508087</v>
       </c>
       <c r="AZ24" t="n">
         <v>1</v>
@@ -4929,7 +4929,7 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.1241</v>
       </c>
     </row>
     <row r="25">
@@ -4987,13 +4987,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.178</v>
+        <v>2.213</v>
       </c>
       <c r="Q25" t="n">
-        <v>2735</v>
+        <v>2692</v>
       </c>
       <c r="R25" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="S25" t="n">
         <v>6</v>
@@ -5172,7 +5172,7 @@
         <v>0.102</v>
       </c>
       <c r="Q26" t="n">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="R26" t="n">
         <v>20.3</v>
@@ -5349,13 +5349,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.916</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>5281</v>
+        <v>5169</v>
       </c>
       <c r="R27" t="n">
-        <v>42.4</v>
+        <v>41.5</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5531,13 +5531,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.389</v>
+        <v>0.392</v>
       </c>
       <c r="Q28" t="n">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="R28" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="S28" t="n">
         <v>246</v>
@@ -5713,13 +5713,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.046</v>
+        <v>0.048</v>
       </c>
       <c r="Q29" t="n">
-        <v>917</v>
+        <v>881</v>
       </c>
       <c r="R29" t="n">
-        <v>98</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.268</v>
+        <v>0.267</v>
       </c>
       <c r="Q30" t="n">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="R30" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="S30" t="n">
         <v>12</v>
@@ -6080,10 +6080,10 @@
         <v>0.002</v>
       </c>
       <c r="Q31" t="n">
-        <v>347948</v>
+        <v>346861</v>
       </c>
       <c r="R31" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="S31" t="n">
         <v>7</v>
@@ -6259,13 +6259,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="Q32" t="n">
-        <v>3485</v>
+        <v>3457</v>
       </c>
       <c r="R32" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="S32" t="n">
         <v>-4</v>
@@ -6441,13 +6441,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="Q33" t="n">
-        <v>5030</v>
+        <v>5197</v>
       </c>
       <c r="R33" t="n">
-        <v>32.8</v>
+        <v>33.9</v>
       </c>
       <c r="S33" t="n">
         <v>-25</v>
@@ -6623,13 +6623,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.052</v>
+        <v>0.053</v>
       </c>
       <c r="Q34" t="n">
-        <v>2070</v>
+        <v>2057</v>
       </c>
       <c r="R34" t="n">
-        <v>47.5</v>
+        <v>47.2</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -6805,13 +6805,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
       <c r="Q35" t="n">
-        <v>3262</v>
+        <v>3221</v>
       </c>
       <c r="R35" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="S35" t="n">
         <v>17</v>
@@ -6987,13 +6987,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.149</v>
+        <v>0.146</v>
       </c>
       <c r="Q36" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="R36" t="n">
-        <v>24.1</v>
+        <v>24.8</v>
       </c>
       <c r="S36" t="n">
         <v>12</v>
@@ -7169,13 +7169,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.158</v>
+        <v>0.16</v>
       </c>
       <c r="Q37" t="n">
-        <v>786</v>
+        <v>773</v>
       </c>
       <c r="R37" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="S37" t="n">
         <v>185</v>
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.499</v>
+        <v>0.498</v>
       </c>
       <c r="Q38" t="n">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="R38" t="n">
         <v>15</v>
@@ -7531,13 +7531,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.281</v>
+        <v>0.285</v>
       </c>
       <c r="Q39" t="n">
-        <v>3641</v>
+        <v>3581</v>
       </c>
       <c r="R39" t="n">
-        <v>25.5</v>
+        <v>25</v>
       </c>
       <c r="S39" t="n">
         <v>2</v>
@@ -7893,10 +7893,10 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.784</v>
+        <v>1.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
@@ -8073,13 +8073,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.188</v>
+        <v>0.189</v>
       </c>
       <c r="Q42" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="R42" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S42" t="n">
         <v>19</v>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.1</v>
+        <v>0.099</v>
       </c>
       <c r="Q43" t="n">
-        <v>1486</v>
+        <v>1500</v>
       </c>
       <c r="R43" t="n">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="S43" t="n">
         <v>6</v>
@@ -8437,13 +8437,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.611</v>
+        <v>0.61</v>
       </c>
       <c r="Q44" t="n">
-        <v>1780</v>
+        <v>1783</v>
       </c>
       <c r="R44" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="S44" t="n">
         <v>39</v>
@@ -8622,10 +8622,10 @@
         <v>0.038</v>
       </c>
       <c r="Q45" t="n">
-        <v>806</v>
+        <v>820</v>
       </c>
       <c r="R45" t="n">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="n">
@@ -8793,13 +8793,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="Q46" t="n">
-        <v>1531</v>
+        <v>1509</v>
       </c>
       <c r="R46" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="S46" t="n">
         <v>13</v>
@@ -8975,13 +8975,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="Q47" t="n">
-        <v>1910</v>
+        <v>1894</v>
       </c>
       <c r="R47" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="S47" t="n">
         <v>-3</v>
@@ -9157,13 +9157,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.275</v>
+        <v>0.276</v>
       </c>
       <c r="Q48" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="R48" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="S48" t="n">
         <v>16</v>
@@ -9342,10 +9342,10 @@
         <v>0.056</v>
       </c>
       <c r="Q49" t="n">
-        <v>845</v>
+        <v>836</v>
       </c>
       <c r="R49" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -10323,23 +10323,23 @@
         <v>14.1</v>
       </c>
       <c r="D24" t="n">
-        <v>12.47</v>
+        <v>12.52</v>
       </c>
       <c r="E24" t="n">
-        <v>13.1</v>
+        <v>12.6</v>
       </c>
       <c r="F24" t="n">
         <v>69.12</v>
       </c>
       <c r="G24" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="H24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-08/enriched_analysis.xlsx
+++ b/output/2026-09-08/enriched_analysis.xlsx
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.418</v>
+        <v>0.415</v>
       </c>
       <c r="Q3" t="n">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="R3" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="S3" t="n">
         <v>19</v>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>3.006</v>
       </c>
       <c r="Q4" t="n">
-        <v>2746</v>
+        <v>2741</v>
       </c>
       <c r="R4" t="n">
         <v>21.5</v>
@@ -1544,7 +1544,7 @@
         <v>0.043</v>
       </c>
       <c r="Q6" t="n">
-        <v>16686</v>
+        <v>16675</v>
       </c>
       <c r="R6" t="n">
         <v>42.5</v>
@@ -2085,13 +2085,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.638</v>
+        <v>0.647</v>
       </c>
       <c r="Q9" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="R9" t="n">
-        <v>8.779999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="S9" t="n">
         <v>17</v>
@@ -2473,7 +2473,7 @@
         <v>11.6</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y11" t="b">
         <v>1</v>
@@ -3175,13 +3175,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.619</v>
+        <v>0.617</v>
       </c>
       <c r="Q15" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="R15" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="S15" t="n">
         <v>21</v>
@@ -3357,13 +3357,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.133</v>
+        <v>0.134</v>
       </c>
       <c r="Q16" t="n">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="R16" t="n">
-        <v>6.09</v>
+        <v>6.04</v>
       </c>
       <c r="S16" t="n">
         <v>118</v>
@@ -3720,10 +3720,10 @@
         <v>0.124</v>
       </c>
       <c r="Q18" t="n">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="R18" t="n">
-        <v>8.880000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="S18" t="n">
         <v>7</v>
@@ -4263,13 +4263,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.188</v>
+        <v>0.187</v>
       </c>
       <c r="Q21" t="n">
-        <v>1604</v>
+        <v>1608</v>
       </c>
       <c r="R21" t="n">
-        <v>55.9</v>
+        <v>56.1</v>
       </c>
       <c r="S21" t="n">
         <v>7</v>
@@ -4284,7 +4284,7 @@
         <v>0.95</v>
       </c>
       <c r="W21" t="n">
-        <v>5.28</v>
+        <v>5.75</v>
       </c>
       <c r="X21" t="n">
         <v>0.52</v>
@@ -5010,7 +5010,7 @@
         <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>3.08</v>
+        <v>3.17</v>
       </c>
       <c r="X25" t="n">
         <v>0.06</v>
@@ -5171,13 +5171,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>5187</v>
+        <v>5173</v>
       </c>
       <c r="R26" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5377,7 +5377,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y27" t="b">
         <v>1</v>
@@ -5535,10 +5535,10 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.397</v>
+        <v>0.394</v>
       </c>
       <c r="Q28" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="R28" t="n">
         <v>104</v>
@@ -5717,13 +5717,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.16</v>
+        <v>0.161</v>
       </c>
       <c r="Q29" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R29" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="S29" t="n">
         <v>12</v>
@@ -5741,7 +5741,7 @@
         <v>7.91</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y29" t="b">
         <v>0</v>
@@ -5899,13 +5899,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.857</v>
+        <v>0.849</v>
       </c>
       <c r="Q30" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R30" t="n">
-        <v>75.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="S30" t="n">
         <v>-1</v>
@@ -6263,13 +6263,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="Q32" t="n">
-        <v>348924</v>
+        <v>346751</v>
       </c>
       <c r="R32" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="S32" t="n">
         <v>7</v>
@@ -6469,7 +6469,7 @@
         <v>10.7</v>
       </c>
       <c r="X33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="b">
         <v>1</v>
@@ -7172,10 +7172,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="Q37" t="n">
-        <v>56015</v>
+        <v>55835</v>
       </c>
       <c r="R37" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -8619,10 +8619,10 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.595</v>
+        <v>0.594</v>
       </c>
       <c r="Q45" t="n">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="R45" t="n">
         <v>33</v>
@@ -9160,7 +9160,7 @@
         <v>0.042</v>
       </c>
       <c r="Q48" t="n">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="R48" t="n">
         <v>20</v>

--- a/output/2026-09-08/enriched_analysis.xlsx
+++ b/output/2026-09-08/enriched_analysis.xlsx
@@ -4762,7 +4762,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
+          <t>PNGS Reva Diamond Jewellery Limited</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
+          <t>PNGS Reva Diamond Jewellery Limited</t>
         </is>
       </c>
       <c r="C24" t="n">

--- a/output/2026-09-08/enriched_analysis.xlsx
+++ b/output/2026-09-08/enriched_analysis.xlsx
@@ -766,7 +766,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gandhar Oil Refinery (India) Limited</t>
+          <t>GANDHAR OIL REFINERY (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.077</v>
+        <v>0.076</v>
       </c>
       <c r="Q2" t="n">
-        <v>2585</v>
+        <v>2618</v>
       </c>
       <c r="R2" t="n">
-        <v>8.880000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="S2" t="n">
         <v>36</v>
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.415</v>
+        <v>0.417</v>
       </c>
       <c r="Q3" t="n">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="R3" t="n">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="S3" t="n">
         <v>19</v>
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.006</v>
+        <v>2.789</v>
       </c>
       <c r="Q4" t="n">
-        <v>2741</v>
+        <v>2954</v>
       </c>
       <c r="R4" t="n">
-        <v>21.5</v>
+        <v>23.2</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -1359,13 +1359,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.056</v>
+        <v>0.059</v>
       </c>
       <c r="Q5" t="n">
-        <v>1473</v>
+        <v>1385</v>
       </c>
       <c r="R5" t="n">
-        <v>19.8</v>
+        <v>18.6</v>
       </c>
       <c r="S5" t="n">
         <v>55</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>THANGAMAIYL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.043</v>
+        <v>0.045</v>
       </c>
       <c r="Q6" t="n">
-        <v>16675</v>
+        <v>16175</v>
       </c>
       <c r="R6" t="n">
-        <v>42.5</v>
+        <v>41.2</v>
       </c>
       <c r="S6" t="n">
         <v>83</v>
@@ -1726,10 +1726,10 @@
         <v>0.048</v>
       </c>
       <c r="Q7" t="n">
-        <v>15891</v>
+        <v>15909</v>
       </c>
       <c r="R7" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="S7" t="n">
         <v>16</v>
@@ -1908,7 +1908,7 @@
         <v>0.006</v>
       </c>
       <c r="Q8" t="n">
-        <v>4322</v>
+        <v>4307</v>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
@@ -2085,13 +2085,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.647</v>
+        <v>0.623</v>
       </c>
       <c r="Q9" t="n">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="R9" t="n">
-        <v>8.66</v>
+        <v>9.02</v>
       </c>
       <c r="S9" t="n">
         <v>17</v>
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.301</v>
+        <v>0.308</v>
       </c>
       <c r="Q10" t="n">
-        <v>2816</v>
+        <v>2757</v>
       </c>
       <c r="R10" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -2449,13 +2449,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.164</v>
+        <v>0.159</v>
       </c>
       <c r="Q11" t="n">
-        <v>676</v>
+        <v>699</v>
       </c>
       <c r="R11" t="n">
-        <v>56.5</v>
+        <v>58.4</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -2473,7 +2473,7 @@
         <v>11.6</v>
       </c>
       <c r="X11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="b">
         <v>1</v>
@@ -2816,7 +2816,7 @@
         <v>0.007</v>
       </c>
       <c r="Q13" t="n">
-        <v>5936</v>
+        <v>5911</v>
       </c>
       <c r="R13" t="n">
         <v>10</v>
@@ -2943,12 +2943,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2972,22 +2972,22 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>972.75</v>
+        <v>84.03</v>
       </c>
       <c r="J14" t="n">
-        <v>734.17</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>32.5</v>
+        <v>5.5</v>
       </c>
       <c r="L14" t="n">
-        <v>61.71</v>
+        <v>62.78</v>
       </c>
       <c r="M14" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -2995,50 +2995,52 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.708</v>
+        <v>0.441</v>
       </c>
       <c r="Q14" t="n">
-        <v>301</v>
-      </c>
-      <c r="R14" t="inlineStr"/>
+        <v>429</v>
+      </c>
+      <c r="R14" t="n">
+        <v>39.8</v>
+      </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="T14" t="n">
-        <v>11.91</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-184</v>
+        <v>-19</v>
       </c>
       <c r="V14" t="n">
-        <v>31.98</v>
+        <v>1.54</v>
       </c>
       <c r="W14" t="n">
-        <v>0.27</v>
+        <v>8.73</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1</v>
+        <v>0.28</v>
       </c>
       <c r="Y14" t="b">
         <v>1</v>
       </c>
       <c r="Z14" t="n">
-        <v>57.93</v>
+        <v>41.64</v>
       </c>
       <c r="AA14" t="n">
-        <v>737.3200000000001</v>
+        <v>76.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>764.83</v>
+        <v>78.16</v>
       </c>
       <c r="AC14" t="n">
-        <v>23.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>725.7771441605839</v>
+        <v>79.6803132188621</v>
       </c>
       <c r="AE14" t="n">
-        <v>34</v>
+        <v>5.5</v>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
@@ -3052,12 +3054,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>09-06-2026</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -3066,49 +3068,49 @@
         </is>
       </c>
       <c r="AK14" t="n">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="AL14" t="n">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="AM14" t="n">
         <v>4</v>
       </c>
       <c r="AN14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AP14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR14" t="n">
         <v>5</v>
       </c>
       <c r="AS14" t="n">
-        <v>5174686</v>
+        <v>2010254</v>
       </c>
       <c r="AT14" t="n">
-        <v>5174686</v>
+        <v>14951696</v>
       </c>
       <c r="AU14" t="n">
-        <v>28636263</v>
+        <v>14951696</v>
       </c>
       <c r="AV14" t="n">
-        <v>28636263</v>
+        <v>14951696</v>
       </c>
       <c r="AW14" t="n">
-        <v>28636263</v>
+        <v>16633076</v>
       </c>
       <c r="AX14" t="n">
-        <v>5174686</v>
+        <v>2010254</v>
       </c>
       <c r="AY14" t="n">
-        <v>28636263</v>
+        <v>14951696</v>
       </c>
       <c r="AZ14" t="n">
         <v>1</v>
@@ -3117,18 +3119,18 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.1807</v>
+        <v>0.1344</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3152,22 +3154,22 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>84.03</v>
+        <v>972.75</v>
       </c>
       <c r="J15" t="n">
-        <v>78.09</v>
+        <v>734.17</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6</v>
+        <v>32.5</v>
       </c>
       <c r="L15" t="n">
-        <v>62.78</v>
+        <v>61.71</v>
       </c>
       <c r="M15" t="n">
-        <v>2.66</v>
+        <v>2.13</v>
       </c>
       <c r="N15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3175,52 +3177,50 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.617</v>
+        <v>0.605</v>
       </c>
       <c r="Q15" t="n">
-        <v>431</v>
-      </c>
-      <c r="R15" t="n">
-        <v>40</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="T15" t="n">
-        <v>8.390000000000001</v>
+        <v>11.91</v>
       </c>
       <c r="U15" t="n">
-        <v>-19</v>
+        <v>-184</v>
       </c>
       <c r="V15" t="n">
-        <v>1.54</v>
+        <v>31.98</v>
       </c>
       <c r="W15" t="n">
-        <v>8.73</v>
+        <v>0.27</v>
       </c>
       <c r="X15" t="n">
-        <v>0.28</v>
+        <v>0.1</v>
       </c>
       <c r="Y15" t="b">
         <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>41.64</v>
+        <v>57.93</v>
       </c>
       <c r="AA15" t="n">
-        <v>76.5</v>
+        <v>737.3200000000001</v>
       </c>
       <c r="AB15" t="n">
-        <v>78.16</v>
+        <v>764.83</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.199999999999999</v>
+        <v>23.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>78.09219155280819</v>
+        <v>725.7771441605839</v>
       </c>
       <c r="AE15" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>05-06-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -3248,49 +3248,49 @@
         </is>
       </c>
       <c r="AK15" t="n">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="AL15" t="n">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="AM15" t="n">
         <v>4</v>
       </c>
       <c r="AN15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AP15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR15" t="n">
         <v>5</v>
       </c>
       <c r="AS15" t="n">
-        <v>2010254</v>
+        <v>5174686</v>
       </c>
       <c r="AT15" t="n">
-        <v>14951696</v>
+        <v>5174686</v>
       </c>
       <c r="AU15" t="n">
-        <v>14951696</v>
+        <v>28636263</v>
       </c>
       <c r="AV15" t="n">
-        <v>14951696</v>
+        <v>28636263</v>
       </c>
       <c r="AW15" t="n">
-        <v>16633076</v>
+        <v>28636263</v>
       </c>
       <c r="AX15" t="n">
-        <v>2010254</v>
+        <v>5174686</v>
       </c>
       <c r="AY15" t="n">
-        <v>14951696</v>
+        <v>28636263</v>
       </c>
       <c r="AZ15" t="n">
         <v>1</v>
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.1344</v>
+        <v>0.1807</v>
       </c>
     </row>
     <row r="16">
@@ -3357,13 +3357,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.134</v>
+        <v>0.136</v>
       </c>
       <c r="Q16" t="n">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="R16" t="n">
-        <v>6.04</v>
+        <v>5.92</v>
       </c>
       <c r="S16" t="n">
         <v>118</v>
@@ -3535,13 +3535,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.305</v>
+        <v>0.306</v>
       </c>
       <c r="Q17" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="R17" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="S17" t="n">
         <v>21</v>
@@ -3717,13 +3717,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.124</v>
+        <v>0.122</v>
       </c>
       <c r="Q18" t="n">
-        <v>906</v>
+        <v>920</v>
       </c>
       <c r="R18" t="n">
-        <v>8.91</v>
+        <v>9.06</v>
       </c>
       <c r="S18" t="n">
         <v>7</v>
@@ -3899,13 +3899,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0.098</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>265</v>
+        <v>306</v>
       </c>
       <c r="R19" t="n">
-        <v>28.4</v>
+        <v>32.8</v>
       </c>
       <c r="S19" t="n">
         <v>24</v>
@@ -4029,12 +4029,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>BAJAJHCARE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>BAJAJ HEALTHCARE LIMITED</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4046,160 +4046,160 @@
         </is>
       </c>
       <c r="E20" t="n">
+        <v>22</v>
+      </c>
+      <c r="F20" t="n">
+        <v>21</v>
+      </c>
+      <c r="G20" t="n">
+        <v>15</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>336.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>297.3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>67.69</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>12-06-2026</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1120</v>
+      </c>
+      <c r="R20" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="S20" t="n">
+        <v>12</v>
+      </c>
+      <c r="T20" t="n">
+        <v>29</v>
+      </c>
+      <c r="U20" t="n">
         <v>20</v>
       </c>
-      <c r="F20" t="n">
-        <v>15</v>
-      </c>
-      <c r="G20" t="n">
-        <v>25</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-2</v>
-      </c>
-      <c r="I20" t="n">
-        <v>601.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>589.6</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="M20" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="N20" t="n">
-        <v>40</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>31-08-2026</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>0.508</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1107</v>
-      </c>
-      <c r="R20" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>21</v>
-      </c>
-      <c r="T20" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="U20" t="n">
-        <v>23</v>
-      </c>
       <c r="V20" t="n">
-        <v>-0.07000000000000001</v>
+        <v>4.07</v>
       </c>
       <c r="W20" t="n">
-        <v>1.58</v>
+        <v>11.5</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="Y20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="n">
-        <v>-110</v>
+        <v>17</v>
       </c>
       <c r="AA20" t="n">
-        <v>575.04</v>
+        <v>334.58</v>
       </c>
       <c r="AB20" t="n">
-        <v>510.78</v>
+        <v>345.82</v>
       </c>
       <c r="AC20" t="n">
-        <v>14.2</v>
+        <v>6</v>
       </c>
       <c r="AD20" t="n">
-        <v>578.7647399321921</v>
+        <v>297.30147</v>
       </c>
       <c r="AE20" t="n">
-        <v>3.9</v>
+        <v>13.3</v>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>04-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
         <v>88</v>
       </c>
-      <c r="AL20" t="n">
-        <v>96</v>
-      </c>
       <c r="AM20" t="n">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="AN20" t="n">
         <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="AS20" t="n">
         <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>6154897</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>19212594</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>19212594</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>47177030</v>
+        <v>29730147</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>19212594</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA20" t="n">
         <v>0</v>
@@ -4263,13 +4263,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.187</v>
+        <v>0.188</v>
       </c>
       <c r="Q21" t="n">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="R21" t="n">
-        <v>56.1</v>
+        <v>56</v>
       </c>
       <c r="S21" t="n">
         <v>7</v>
@@ -4393,12 +4393,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BAJAJHCARE</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BAJAJ HEALTHCARE LIMITED</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -4410,160 +4410,160 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
+        <v>15</v>
+      </c>
+      <c r="G22" t="n">
+        <v>25</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>601.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>598.17</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="N22" t="n">
+        <v>36</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1091</v>
+      </c>
+      <c r="R22" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="S22" t="n">
         <v>21</v>
       </c>
-      <c r="G22" t="n">
-        <v>15</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>336.7</v>
-      </c>
-      <c r="J22" t="n">
-        <v>297.3</v>
-      </c>
-      <c r="K22" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="L22" t="n">
-        <v>67.69</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>12-06-2026</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>0.262</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1133</v>
-      </c>
-      <c r="R22" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>12</v>
-      </c>
       <c r="T22" t="n">
-        <v>29</v>
+        <v>-0.11</v>
       </c>
       <c r="U22" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="V22" t="n">
-        <v>4.07</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>11.5</v>
+        <v>1.58</v>
       </c>
       <c r="X22" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>17</v>
+        <v>-110</v>
       </c>
       <c r="AA22" t="n">
-        <v>334.58</v>
+        <v>575.04</v>
       </c>
       <c r="AB22" t="n">
-        <v>345.82</v>
+        <v>510.78</v>
       </c>
       <c r="AC22" t="n">
-        <v>6</v>
+        <v>14.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>297.30147</v>
+        <v>592.9971152911179</v>
       </c>
       <c r="AE22" t="n">
-        <v>13.3</v>
+        <v>1.4</v>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AL22" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AM22" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="AN22" t="n">
         <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AR22" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AS22" t="n">
         <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>6154897</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>19212594</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>19212594</v>
       </c>
       <c r="AW22" t="n">
-        <v>29730147</v>
+        <v>47177030</v>
       </c>
       <c r="AX22" t="n">
         <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>19212594</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA22" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
         <v>318.1</v>
       </c>
       <c r="J23" t="n">
-        <v>314.32</v>
+        <v>314.44</v>
       </c>
       <c r="K23" t="n">
         <v>1.2</v>
@@ -4616,24 +4616,24 @@
         <v>63.24</v>
       </c>
       <c r="M23" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="N23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.58</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="Q23" t="n">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="R23" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="S23" t="n">
         <v>22</v>
@@ -4669,14 +4669,14 @@
         <v>15.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>316.1468258224667</v>
+        <v>316.2199031834839</v>
       </c>
       <c r="AE23" t="n">
         <v>0.6</v>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -4696,53 +4696,53 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="AK23" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="AL23" t="n">
         <v>46</v>
       </c>
       <c r="AM23" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AP23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>336800</v>
       </c>
       <c r="AT23" t="n">
-        <v>6508340</v>
+        <v>6845140</v>
       </c>
       <c r="AU23" t="n">
-        <v>6508340</v>
+        <v>6845140</v>
       </c>
       <c r="AV23" t="n">
-        <v>20632058</v>
+        <v>20968858</v>
       </c>
       <c r="AW23" t="n">
-        <v>20632058</v>
+        <v>20968858</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>336800</v>
       </c>
       <c r="AY23" t="n">
-        <v>6508340</v>
+        <v>6845140</v>
       </c>
       <c r="AZ23" t="n">
         <v>2</v>
@@ -4751,7 +4751,7 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>0.0492</v>
       </c>
     </row>
     <row r="24">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PNGS Reva Diamond Jewellery Limited</t>
+          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4809,13 +4809,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.101</v>
+        <v>0.105</v>
       </c>
       <c r="Q24" t="n">
-        <v>1729</v>
+        <v>1659</v>
       </c>
       <c r="R24" t="n">
-        <v>20.5</v>
+        <v>19.6</v>
       </c>
       <c r="S24" t="n">
         <v>581</v>
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.203</v>
+        <v>2.206</v>
       </c>
       <c r="Q25" t="n">
-        <v>2704</v>
+        <v>2701</v>
       </c>
       <c r="R25" t="n">
         <v>212</v>
@@ -5171,13 +5171,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.947</v>
       </c>
       <c r="Q26" t="n">
-        <v>5173</v>
+        <v>5111</v>
       </c>
       <c r="R26" t="n">
-        <v>41.5</v>
+        <v>41</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5359,7 +5359,7 @@
         <v>901</v>
       </c>
       <c r="R27" t="n">
-        <v>96.3</v>
+        <v>96.2</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -5377,7 +5377,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="X27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="b">
         <v>1</v>
@@ -5535,13 +5535,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.394</v>
+        <v>0.39</v>
       </c>
       <c r="Q28" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="R28" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="S28" t="n">
         <v>246</v>
@@ -5717,13 +5717,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.161</v>
+        <v>0.157</v>
       </c>
       <c r="Q29" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="R29" t="n">
-        <v>24</v>
+        <v>24.4</v>
       </c>
       <c r="S29" t="n">
         <v>12</v>
@@ -5741,7 +5741,7 @@
         <v>7.91</v>
       </c>
       <c r="X29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="b">
         <v>0</v>
@@ -5879,19 +5879,19 @@
         <v>27.45</v>
       </c>
       <c r="J30" t="n">
-        <v>29.78</v>
+        <v>29.82</v>
       </c>
       <c r="K30" t="n">
-        <v>-7.8</v>
+        <v>-7.9</v>
       </c>
       <c r="L30" t="n">
         <v>69.03</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="N30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -5899,13 +5899,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.849</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="R30" t="n">
-        <v>76.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="S30" t="n">
         <v>-1</v>
@@ -5941,10 +5941,10 @@
         <v>28.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>29.73921840029116</v>
+        <v>29.77378953659848</v>
       </c>
       <c r="AE30" t="n">
-        <v>-7.7</v>
+        <v>-7.8</v>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>09-06-2026</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="AK30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL30" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AM30" t="n">
         <v>75</v>
@@ -6081,13 +6081,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="Q31" t="n">
-        <v>3449</v>
+        <v>3658</v>
       </c>
       <c r="R31" t="n">
-        <v>20.4</v>
+        <v>21.6</v>
       </c>
       <c r="S31" t="n">
         <v>-4</v>
@@ -6266,10 +6266,10 @@
         <v>0.002</v>
       </c>
       <c r="Q32" t="n">
-        <v>346751</v>
+        <v>334921</v>
       </c>
       <c r="R32" t="n">
-        <v>19.1</v>
+        <v>18.4</v>
       </c>
       <c r="S32" t="n">
         <v>7</v>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>5158</v>
+        <v>5252</v>
       </c>
       <c r="R33" t="n">
-        <v>33.6</v>
+        <v>34.3</v>
       </c>
       <c r="S33" t="n">
         <v>-25</v>
@@ -6607,27 +6607,27 @@
         <v>14.06</v>
       </c>
       <c r="J34" t="n">
-        <v>12.52</v>
+        <v>12.58</v>
       </c>
       <c r="K34" t="n">
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
       <c r="L34" t="n">
         <v>69.12</v>
       </c>
       <c r="M34" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="N34" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.425</v>
+        <v>0.445</v>
       </c>
       <c r="Q34" t="n">
         <v>398</v>
@@ -6665,10 +6665,10 @@
         <v>-5</v>
       </c>
       <c r="AD34" t="n">
-        <v>12.47706136306301</v>
+        <v>12.53656631009912</v>
       </c>
       <c r="AE34" t="n">
-        <v>12.7</v>
+        <v>12.2</v>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
@@ -6692,53 +6692,53 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="AK34" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL34" t="n">
         <v>29</v>
       </c>
       <c r="AM34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP34" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ34" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR34" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS34" t="n">
-        <v>2172554</v>
+        <v>2924891</v>
       </c>
       <c r="AT34" t="n">
-        <v>5396634</v>
+        <v>6148971</v>
       </c>
       <c r="AU34" t="n">
-        <v>17508087</v>
+        <v>18260424</v>
       </c>
       <c r="AV34" t="n">
-        <v>17508087</v>
+        <v>18260424</v>
       </c>
       <c r="AW34" t="n">
-        <v>17508087</v>
+        <v>18260424</v>
       </c>
       <c r="AX34" t="n">
-        <v>2172554</v>
+        <v>2924891</v>
       </c>
       <c r="AY34" t="n">
-        <v>17508087</v>
+        <v>18260424</v>
       </c>
       <c r="AZ34" t="n">
         <v>1</v>
@@ -6747,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>0.1241</v>
+        <v>0.1602</v>
       </c>
     </row>
     <row r="35">
@@ -6805,13 +6805,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="Q35" t="n">
-        <v>2045</v>
+        <v>2062</v>
       </c>
       <c r="R35" t="n">
-        <v>46.9</v>
+        <v>47.3</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -6990,10 +6990,10 @@
         <v>0.034</v>
       </c>
       <c r="Q36" t="n">
-        <v>3239</v>
+        <v>3208</v>
       </c>
       <c r="R36" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="S36" t="n">
         <v>17</v>
@@ -7172,10 +7172,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="Q37" t="n">
-        <v>55835</v>
+        <v>55391</v>
       </c>
       <c r="R37" t="n">
-        <v>47.3</v>
+        <v>46.9</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -7351,13 +7351,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.165</v>
+        <v>0.159</v>
       </c>
       <c r="Q38" t="n">
-        <v>750</v>
+        <v>778</v>
       </c>
       <c r="R38" t="n">
-        <v>13.6</v>
+        <v>14.1</v>
       </c>
       <c r="S38" t="n">
         <v>185</v>
@@ -7531,13 +7531,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.498</v>
+        <v>0.503</v>
       </c>
       <c r="Q39" t="n">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="R39" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="S39" t="n">
         <v>-1</v>
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.287</v>
+        <v>0.283</v>
       </c>
       <c r="Q41" t="n">
-        <v>3563</v>
+        <v>3614</v>
       </c>
       <c r="R41" t="n">
-        <v>24.9</v>
+        <v>25.3</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.128</v>
+        <v>0.127</v>
       </c>
       <c r="Q42" t="n">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="R42" t="n">
         <v>13.8</v>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.19</v>
+        <v>0.191</v>
       </c>
       <c r="Q43" t="n">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="R43" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S43" t="n">
         <v>19</v>
@@ -8437,13 +8437,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.099</v>
+        <v>0.096</v>
       </c>
       <c r="Q44" t="n">
-        <v>1500</v>
+        <v>1539</v>
       </c>
       <c r="R44" t="n">
-        <v>13.6</v>
+        <v>13.9</v>
       </c>
       <c r="S44" t="n">
         <v>6</v>
@@ -8619,13 +8619,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.594</v>
+        <v>0.607</v>
       </c>
       <c r="Q45" t="n">
-        <v>1829</v>
+        <v>1790</v>
       </c>
       <c r="R45" t="n">
-        <v>33</v>
+        <v>32.3</v>
       </c>
       <c r="S45" t="n">
         <v>39</v>
@@ -8801,13 +8801,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="Q46" t="n">
-        <v>795</v>
+        <v>829</v>
       </c>
       <c r="R46" t="n">
-        <v>19.1</v>
+        <v>19.9</v>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="n">
@@ -8975,13 +8975,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="Q47" t="n">
-        <v>1533</v>
+        <v>1520</v>
       </c>
       <c r="R47" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="S47" t="n">
         <v>13</v>
@@ -9160,10 +9160,10 @@
         <v>0.042</v>
       </c>
       <c r="Q48" t="n">
-        <v>1892</v>
+        <v>1875</v>
       </c>
       <c r="R48" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="S48" t="n">
         <v>-3</v>
@@ -9328,10 +9328,10 @@
         <v>61.81</v>
       </c>
       <c r="M49" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="N49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -9339,13 +9339,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0.276</v>
+        <v>0.264</v>
       </c>
       <c r="Q49" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="R49" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="S49" t="n">
         <v>16</v>
@@ -9381,7 +9381,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD49" t="n">
-        <v>34.64380341880342</v>
+        <v>34.63651339285714</v>
       </c>
       <c r="AE49" t="n">
         <v>-19.7</v>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>05-06-2026</t>
+          <t>10-06-2026</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -9412,10 +9412,10 @@
         </is>
       </c>
       <c r="AK49" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL49" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM49" t="n">
         <v>15</v>
@@ -9521,13 +9521,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0.056</v>
+        <v>0.055</v>
       </c>
       <c r="Q50" t="n">
-        <v>834</v>
+        <v>857</v>
       </c>
       <c r="R50" t="n">
-        <v>22.7</v>
+        <v>23.4</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gandhar Oil Refinery (India) Limited</t>
+          <t>GANDHAR OIL REFINERY (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>THANGAMAIYL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -10143,31 +10143,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>972.75</v>
+        <v>84.03</v>
       </c>
       <c r="D14" t="n">
-        <v>734.17</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>32.5</v>
+        <v>5.5</v>
       </c>
       <c r="F14" t="n">
-        <v>61.71</v>
+        <v>62.78</v>
       </c>
       <c r="G14" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -10178,31 +10178,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>84.03</v>
+        <v>972.75</v>
       </c>
       <c r="D15" t="n">
-        <v>78.09</v>
+        <v>734.17</v>
       </c>
       <c r="E15" t="n">
-        <v>7.6</v>
+        <v>32.5</v>
       </c>
       <c r="F15" t="n">
-        <v>62.78</v>
+        <v>61.71</v>
       </c>
       <c r="G15" t="n">
-        <v>2.66</v>
+        <v>2.13</v>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -10353,35 +10353,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>BAJAJHCARE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>BAJAJ HEALTHCARE LIMITED</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>601.4</v>
+        <v>336.7</v>
       </c>
       <c r="D20" t="n">
-        <v>589.6</v>
+        <v>297.3</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>13.3</v>
       </c>
       <c r="F20" t="n">
-        <v>64.68000000000001</v>
+        <v>67.69</v>
       </c>
       <c r="G20" t="n">
-        <v>5.62</v>
+        <v>2.97</v>
       </c>
       <c r="H20" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
     </row>
@@ -10423,35 +10423,35 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BAJAJHCARE</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BAJAJ HEALTHCARE LIMITED</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>336.7</v>
+        <v>601.4</v>
       </c>
       <c r="D22" t="n">
-        <v>297.3</v>
+        <v>598.17</v>
       </c>
       <c r="E22" t="n">
-        <v>13.3</v>
+        <v>0.5</v>
       </c>
       <c r="F22" t="n">
-        <v>67.69</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>2.97</v>
+        <v>5.22</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
         <v>318.1</v>
       </c>
       <c r="D23" t="n">
-        <v>314.32</v>
+        <v>314.44</v>
       </c>
       <c r="E23" t="n">
         <v>1.2</v>
@@ -10479,14 +10479,14 @@
         <v>63.24</v>
       </c>
       <c r="G23" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="H23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PNGS Reva Diamond Jewellery Limited</t>
+          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -10715,19 +10715,19 @@
         <v>27.45</v>
       </c>
       <c r="D30" t="n">
-        <v>29.78</v>
+        <v>29.82</v>
       </c>
       <c r="E30" t="n">
-        <v>-7.8</v>
+        <v>-7.9</v>
       </c>
       <c r="F30" t="n">
         <v>69.03</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="H30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -10855,23 +10855,23 @@
         <v>14.06</v>
       </c>
       <c r="D34" t="n">
-        <v>12.52</v>
+        <v>12.58</v>
       </c>
       <c r="E34" t="n">
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
       <c r="F34" t="n">
         <v>69.12</v>
       </c>
       <c r="G34" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="H34" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
     </row>
@@ -11389,10 +11389,10 @@
         <v>61.81</v>
       </c>
       <c r="G49" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="H49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
